--- a/data/trans_orig/IMC_inf_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31272</t>
+          <t>31050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48074</t>
+          <t>47156</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53869</t>
+          <t>52679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71860</t>
+          <t>71557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89939</t>
+          <t>88933</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115096</t>
+          <t>114762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70022</t>
+          <t>70940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86824</t>
+          <t>87046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61783</t>
+          <t>62086</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79774</t>
+          <t>80964</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136642</t>
+          <t>136976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161799</t>
+          <t>162805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54557</t>
+          <t>54855</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74044</t>
+          <t>74010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77702</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100364</t>
+          <t>98637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>138489</t>
+          <t>137771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166553</t>
+          <t>167662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96410</t>
+          <t>96444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115897</t>
+          <t>115599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80266</t>
+          <t>81993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102928</t>
+          <t>103773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184531</t>
+          <t>183422</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212595</t>
+          <t>213313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30310</t>
+          <t>30600</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45352</t>
+          <t>46316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45610</t>
+          <t>45132</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63052</t>
+          <t>62894</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79823</t>
+          <t>80957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103691</t>
+          <t>103567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68015</t>
+          <t>67051</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83057</t>
+          <t>82767</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57417</t>
+          <t>57575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74859</t>
+          <t>75337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130145</t>
+          <t>130269</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154013</t>
+          <t>152879</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51142</t>
+          <t>51934</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74516</t>
+          <t>73425</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60253</t>
+          <t>58884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81246</t>
+          <t>79396</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117010</t>
+          <t>117828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146857</t>
+          <t>148500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101639</t>
+          <t>102730</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125013</t>
+          <t>124221</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89465</t>
+          <t>91315</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>110458</t>
+          <t>111827</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>200009</t>
+          <t>198366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>229856</t>
+          <t>229038</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>187155</t>
+          <t>186354</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>221822</t>
+          <t>221172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>255946</t>
+          <t>253811</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>295496</t>
+          <t>293625</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>452143</t>
+          <t>450305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>506013</t>
+          <t>505438</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>356250</t>
+          <t>356900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>390917</t>
+          <t>391718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>309957</t>
+          <t>311828</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349507</t>
+          <t>351642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>677512</t>
+          <t>678087</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>731382</t>
+          <t>733220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,95%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34371</t>
+          <t>34578</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50573</t>
+          <t>50524</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62837</t>
+          <t>62813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84547</t>
+          <t>83975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108836</t>
+          <t>107585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49861</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66063</t>
+          <t>65856</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46065</t>
+          <t>46089</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64490</t>
+          <t>63892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100500</t>
+          <t>101751</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124789</t>
+          <t>125361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,89%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53637</t>
+          <t>54299</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73980</t>
+          <t>73676</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83805</t>
+          <t>82320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104314</t>
+          <t>103395</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142938</t>
+          <t>143820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172785</t>
+          <t>171729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82197</t>
+          <t>82501</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102540</t>
+          <t>101878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63351</t>
+          <t>64270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83860</t>
+          <t>85345</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151057</t>
+          <t>152113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180904</t>
+          <t>180022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,59%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39809</t>
+          <t>39605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56777</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49988</t>
+          <t>49413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68054</t>
+          <t>67784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94689</t>
+          <t>94954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119685</t>
+          <t>118182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60226</t>
+          <t>60450</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77194</t>
+          <t>77398</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56074</t>
+          <t>56344</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>74715</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121445</t>
+          <t>122948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146441</t>
+          <t>146176</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58110</t>
+          <t>56752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78241</t>
+          <t>78029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64642</t>
+          <t>64807</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85698</t>
+          <t>85495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127154</t>
+          <t>128583</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157452</t>
+          <t>157089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75175</t>
+          <t>75387</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95306</t>
+          <t>96664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70218</t>
+          <t>70421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91274</t>
+          <t>91109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151880</t>
+          <t>152243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182178</t>
+          <t>180749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,43%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>201556</t>
+          <t>204318</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239622</t>
+          <t>242337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>260698</t>
+          <t>262113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>298687</t>
+          <t>300282</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>475219</t>
+          <t>474635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>527639</t>
+          <t>526569</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287408</t>
+          <t>284693</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>325474</t>
+          <t>322712</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>257924</t>
+          <t>256329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>295913</t>
+          <t>294498</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>556002</t>
+          <t>557072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>608422</t>
+          <t>609006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,2%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>33038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50138</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45140</t>
+          <t>44538</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61743</t>
+          <t>61995</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83949</t>
+          <t>83320</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107223</t>
+          <t>107659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49415</t>
+          <t>49634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>66515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44493</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61096</t>
+          <t>61698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98566</t>
+          <t>98130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121840</t>
+          <t>122469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,51%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37245</t>
+          <t>36991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54921</t>
+          <t>55009</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69977</t>
+          <t>69942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91510</t>
+          <t>92608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114325</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142974</t>
+          <t>141777</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,52%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>106876</t>
+          <t>106788</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124552</t>
+          <t>124806</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88144</t>
+          <t>87046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109677</t>
+          <t>109712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>198477</t>
+          <t>199674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>227126</t>
+          <t>228610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,95%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33207</t>
+          <t>34164</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49499</t>
+          <t>51038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42784</t>
+          <t>42364</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61478</t>
+          <t>61141</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81579</t>
+          <t>82198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104958</t>
+          <t>105572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73849</t>
+          <t>72310</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90141</t>
+          <t>89184</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72593</t>
+          <t>72930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91287</t>
+          <t>91707</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152462</t>
+          <t>151848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175841</t>
+          <t>175222</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,07%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50199</t>
+          <t>50100</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70532</t>
+          <t>69949</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63639</t>
+          <t>64285</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85011</t>
+          <t>84922</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121932</t>
+          <t>120390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149903</t>
+          <t>149493</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89171</t>
+          <t>89754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109504</t>
+          <t>109603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78962</t>
+          <t>79051</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100334</t>
+          <t>99688</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173773</t>
+          <t>174183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>201744</t>
+          <t>203286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170642</t>
+          <t>170586</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>208172</t>
+          <t>208083</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>241033</t>
+          <t>241538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>280406</t>
+          <t>281183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>425364</t>
+          <t>422726</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>481685</t>
+          <t>477154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336230</t>
+          <t>336319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>373760</t>
+          <t>373816</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>303528</t>
+          <t>302751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>342901</t>
+          <t>342396</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>646651</t>
+          <t>651182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>702972</t>
+          <t>705610</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>22676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38061</t>
+          <t>36784</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32180</t>
+          <t>32632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58331</t>
+          <t>59318</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61155</t>
+          <t>60909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90113</t>
+          <t>89339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59226</t>
+          <t>60503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73821</t>
+          <t>74611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63971</t>
+          <t>62984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90122</t>
+          <t>89670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129476</t>
+          <t>130250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158434</t>
+          <t>158680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38345</t>
+          <t>37399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58777</t>
+          <t>56941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75145</t>
+          <t>76441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104722</t>
+          <t>104485</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119022</t>
+          <t>117834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154215</t>
+          <t>154192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109584</t>
+          <t>111420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>130016</t>
+          <t>130962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111774</t>
+          <t>112011</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>141351</t>
+          <t>140055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>230642</t>
+          <t>230665</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>265835</t>
+          <t>267023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23531</t>
+          <t>26439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60260</t>
+          <t>60001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51572</t>
+          <t>52083</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78690</t>
+          <t>78964</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81993</t>
+          <t>81158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129399</t>
+          <t>128821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,0%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106284</t>
+          <t>106543</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143013</t>
+          <t>140105</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85113</t>
+          <t>84839</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112231</t>
+          <t>111720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>200947</t>
+          <t>201525</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>248353</t>
+          <t>249188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30903</t>
+          <t>31466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50942</t>
+          <t>50617</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44181</t>
+          <t>45876</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65714</t>
+          <t>67113</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81248</t>
+          <t>83446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110982</t>
+          <t>110607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92236</t>
+          <t>92561</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112275</t>
+          <t>111712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84538</t>
+          <t>83139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106071</t>
+          <t>104376</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>182448</t>
+          <t>182823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212182</t>
+          <t>209984</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>71,56%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>138492</t>
+          <t>136345</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>185800</t>
+          <t>185752</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>229878</t>
+          <t>228801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>282178</t>
+          <t>279715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>380194</t>
+          <t>379725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>453554</t>
+          <t>453220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>389570</t>
+          <t>389618</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>436878</t>
+          <t>439025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370674</t>
+          <t>373137</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>422974</t>
+          <t>424051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>774668</t>
+          <t>775002</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>848028</t>
+          <t>848497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_inf_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R2-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>62941</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53047</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>72298</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>39,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>54,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>39276</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31050</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47156</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31302</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>48403</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>33,26%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,93%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>62941</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>52679</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>71557</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>47,1%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88933</t>
+          <t>89814</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114762</t>
+          <t>113911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,25%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70702</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61345</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80596</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>45,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>60,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>78820</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>70940</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>87046</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>69693</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>86794</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>66,74%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>60,07%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>73,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>70702</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>62086</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80964</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>52,9%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136976</t>
+          <t>137827</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162805</t>
+          <t>161924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,32%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>133643</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>133643</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>133643</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>118096</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>118096</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>118096</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>133643</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>133643</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>133643</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>87670</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>76973</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>98036</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>42,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>54,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>64293</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54855</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>74010</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>54455</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>74276</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>37,72%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>32,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>87670</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>76857</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>98637</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>48,54%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137771</t>
+          <t>136726</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167662</t>
+          <t>167120</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>92960</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82594</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>103657</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>57,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>106161</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>96444</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>115599</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>96178</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>115999</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>62,28%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>56,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>67,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>92960</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>81993</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>103773</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>51,46%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183422</t>
+          <t>183964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213313</t>
+          <t>214358</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,06%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>180630</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>180630</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>180630</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>170454</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>170454</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>170454</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>180630</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>180630</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>180630</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>54196</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45847</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>62988</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>44,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>52,29%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>37810</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>30600</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46316</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>31018</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>46950</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>54196</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>45132</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>62894</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>44,99%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80957</t>
+          <t>80654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103567</t>
+          <t>103848</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66273</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>57481</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74622</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>55,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>47,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>61,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>75557</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67051</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>82767</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66417</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>82349</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>66,65%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>59,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>73,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>66273</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>57575</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>75337</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>55,01%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130269</t>
+          <t>129988</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152879</t>
+          <t>153182</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,51%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>120469</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>120469</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>120469</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>113367</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>113367</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>113367</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>120469</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>120469</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>120469</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>70183</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>60098</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>80231</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>62345</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>51934</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>73425</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>51923</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>74356</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>35,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>29,48%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>70183</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>58884</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>79396</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>41,11%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>34,49%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117828</t>
+          <t>117933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148500</t>
+          <t>147622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>100528</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90480</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>110613</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,8%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>113810</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>102730</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>124221</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>101799</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>124232</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>64,61%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>57,79%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>70,52%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>100528</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>91315</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>111827</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>58,89%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>53,49%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>65,51%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>296</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198366</t>
+          <t>199244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>229038</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,0%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170711</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170711</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170711</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>176155</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>176155</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>176155</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170711</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170711</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>274990</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>255865</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>293526</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42,26%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>48,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>203724</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>186354</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>221172</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>186635</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>223096</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,24%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>274990</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>253811</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>293625</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>450305</t>
+          <t>450692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>505438</t>
+          <t>504253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>330463</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>311927</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>349588</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>54,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>51,52%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>57,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>374348</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>356900</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>391718</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>354976</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>391437</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>64,76%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,74%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67,76%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>330463</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>311828</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>351642</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>54,58%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>678087</t>
+          <t>679272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>733220</t>
+          <t>732833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>605453</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>605453</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>605453</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>863</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>578072</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>578072</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>578072</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>605453</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>605453</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>605453</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>53883</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44462</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>62657</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>49,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>42477</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>34578</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>50524</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>34072</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>50034</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>42,29%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>53883</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>45010</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>62813</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>49,48%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83975</t>
+          <t>85077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107585</t>
+          <t>109277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55019</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46245</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64440</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>50,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57957</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49910</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>65856</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50400</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>66362</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>57,71%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>49,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,57%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>55019</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>46089</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>63892</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>50,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101751</t>
+          <t>100059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125361</t>
+          <t>124259</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,36%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>108902</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>108902</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>108902</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>100434</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>100434</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>100434</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>108902</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>108902</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>108902</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>93370</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>82634</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>103692</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>55,69%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>49,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>61,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>63949</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54299</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>73676</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>54075</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>73378</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>40,95%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>47,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>93370</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>82320</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>103395</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>55,69%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143820</t>
+          <t>143795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>171729</t>
+          <t>171690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74295</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>63973</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>85031</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>44,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>38,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>50,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92228</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>82501</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>101878</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>82799</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>102102</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>59,05%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>74295</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>64270</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>85345</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>44,31%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152113</t>
+          <t>152152</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180022</t>
+          <t>180047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>167665</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>167665</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>167665</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>156177</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>156177</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>156177</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>167665</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>167665</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>167665</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>58608</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50106</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>67609</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>40,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>54,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>47949</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39605</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56553</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>40316</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>56620</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>40,98%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>58608</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>49413</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>67784</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>47,22%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94954</t>
+          <t>94351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118182</t>
+          <t>119091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,39%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65520</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56519</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74022</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>52,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>45,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>69054</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>60450</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77398</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>60383</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>76687</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>59,02%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>51,67%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>66,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>65520</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>56344</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74715</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>52,78%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122948</t>
+          <t>122039</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146176</t>
+          <t>146779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,87%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>124128</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>124128</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>124128</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>117003</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>117003</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>117003</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>124128</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>124128</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>124128</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>75130</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>65131</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>85438</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>48,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>41,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>54,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>67792</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>56752</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>78029</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>57698</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>78112</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>44,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>50,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>75130</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>64807</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>85495</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>48,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128583</t>
+          <t>127498</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157089</t>
+          <t>158609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>80786</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>70478</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>90785</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>58,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>85624</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>75387</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>96664</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>75304</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>95718</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>55,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>49,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>80786</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>70421</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>91109</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>51,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152243</t>
+          <t>150723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180749</t>
+          <t>181834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,78%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>155916</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>155916</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>155916</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>153416</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>153416</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>153416</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>155916</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>155916</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>155916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>280991</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>261343</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>301978</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>50,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>46,95%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>54,25%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>222166</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>204318</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>242337</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>205399</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>240883</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>42,15%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>280991</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>262113</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>300282</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>50,48%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>474635</t>
+          <t>475291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>526569</t>
+          <t>532153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>275620</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>254633</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>295268</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>49,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>45,75%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>440</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>304864</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>284693</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>322712</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>286147</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>321631</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>57,85%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>54,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>61,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>275620</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>256329</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>294498</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>49,52%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>557072</t>
+          <t>551488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>609006</t>
+          <t>608350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>556611</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>556611</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>556611</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>757</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>527030</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>527030</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>527030</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>556611</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>556611</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>556611</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>53276</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44332</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>62134</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41,73%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>58,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>41944</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>33038</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>49919</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>32905</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>49526</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>42,13%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>53276</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>44538</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>61995</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,15%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>83486</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107659</t>
+          <t>107783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52960</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44102</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61904</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>41,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>58,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57609</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49634</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>66515</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50027</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>66648</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>57,87%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>49,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>66,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>52960</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>44241</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61698</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,85%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98130</t>
+          <t>98006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122469</t>
+          <t>122303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,43%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>106236</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>106236</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>106236</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>99553</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>99553</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>99553</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>106236</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>106236</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>106236</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>81061</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>69676</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>92718</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>45,12%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>38,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>51,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>46185</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36991</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>55009</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38121</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>56393</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>28,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>81061</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>69942</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>92608</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>45,12%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112841</t>
+          <t>113142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141777</t>
+          <t>142071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>98593</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>86936</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>109978</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>54,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>48,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>61,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>115612</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>106788</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>124806</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>105404</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>123676</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>71,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>98593</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>87046</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>109712</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>54,88%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>199674</t>
+          <t>199380</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>228610</t>
+          <t>228309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>179654</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>179654</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>179654</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>161797</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>161797</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>161797</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>179654</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>179654</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>179654</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>51881</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42990</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>62971</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,07%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>41890</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>34164</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51038</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34582</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>50366</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>41,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>51881</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>42364</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>61141</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>38,7%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82198</t>
+          <t>82417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105572</t>
+          <t>106918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>82190</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>71100</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>91081</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>61,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>53,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>67,93%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>81458</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>72310</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>89184</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>72982</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>88766</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>66,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>58,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>72,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>82190</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>72930</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>91707</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>61,3%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151848</t>
+          <t>150502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175222</t>
+          <t>175003</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>134071</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>134071</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>134071</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>123348</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>123348</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>123348</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>134071</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>134071</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>134071</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>74955</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>63961</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>39,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>59847</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>69949</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>49450</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>70439</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>37,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>74955</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>64285</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>84922</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>45,71%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120390</t>
+          <t>120530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149493</t>
+          <t>149983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,34%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>89018</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78665</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>100012</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>99856</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>89754</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>109603</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>89264</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>110253</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>62,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>89018</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>79051</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>99688</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>54,29%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>174183</t>
+          <t>173693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203286</t>
+          <t>203146</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>163973</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>163973</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>163973</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>159703</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>159703</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>159703</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>163973</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>163973</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>163973</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>261173</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>240456</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>281764</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>41,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>48,25%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>189866</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>170586</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>208083</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>172831</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>207961</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>34,88%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,33%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>261173</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>241538</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>281183</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>422726</t>
+          <t>423582</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>477154</t>
+          <t>476396</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>322761</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>302170</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>343478</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>55,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>51,75%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>58,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>354536</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>336319</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>373816</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>336441</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>371571</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>65,12%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68,67%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>322761</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>302751</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>342396</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>55,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>651182</t>
+          <t>651940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>705610</t>
+          <t>704754</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,46%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>583934</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>583934</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>583934</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>811</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>544402</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>544402</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>544402</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>583934</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>583934</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>583934</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44524</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33377</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>55139</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>40,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>29648</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22676</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36784</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,47%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>46375</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32632</t>
+          <t>22894</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59318</t>
+          <t>37346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>76023</t>
+          <t>74651</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60909</t>
+          <t>61928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89339</t>
+          <t>88424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,64%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66383</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55768</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>77530</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>59,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>67639</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>60503</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>74611</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>69,53%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>75927</t>
+          <t>71310</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62984</t>
+          <t>64091</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89670</t>
+          <t>78543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>143566</t>
+          <t>137693</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130250</t>
+          <t>123920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158680</t>
+          <t>150416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>110907</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>110907</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>110907</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>97287</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>97287</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>97287</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>122302</t>
+          <t>101437</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>122302</t>
+          <t>101437</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>122302</t>
+          <t>101437</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>219589</t>
+          <t>212344</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>219589</t>
+          <t>212344</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>219589</t>
+          <t>212344</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>84249</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>72042</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>99189</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>41,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48,59%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>47325</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>37399</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56941</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>28,11%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88864</t>
+          <t>46593</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76441</t>
+          <t>37798</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104485</t>
+          <t>57506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>136189</t>
+          <t>130843</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117834</t>
+          <t>113944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154192</t>
+          <t>149856</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>119902</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>104962</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>132109</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>51,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>64,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>121036</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>111420</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>130962</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>71,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>127632</t>
+          <t>117902</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112011</t>
+          <t>106989</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140055</t>
+          <t>126697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>248668</t>
+          <t>237804</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>230665</t>
+          <t>218791</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>267023</t>
+          <t>254703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,09%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>204151</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>204151</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>204151</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>168361</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>168361</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>168361</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>216496</t>
+          <t>164495</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>216496</t>
+          <t>164495</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>216496</t>
+          <t>164495</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>384857</t>
+          <t>368647</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>384857</t>
+          <t>368647</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>384857</t>
+          <t>368647</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59102</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46990</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>72558</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>31,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>45507</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26439</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>60001</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,32%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>63719</t>
+          <t>40980</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52083</t>
+          <t>31958</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78964</t>
+          <t>50074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>109226</t>
+          <t>100082</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81158</t>
+          <t>85670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128821</t>
+          <t>116302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>91891</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>78435</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>104003</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>60,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>51,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>68,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>121037</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>106543</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>140105</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>72,68%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>84,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100084</t>
+          <t>94718</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84839</t>
+          <t>85624</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111720</t>
+          <t>103740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>221120</t>
+          <t>186609</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>201525</t>
+          <t>170389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>249188</t>
+          <t>201021</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>150993</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>150993</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>150993</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>166544</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>166544</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>166544</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>163803</t>
+          <t>135698</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>163803</t>
+          <t>135698</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163803</t>
+          <t>135698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>330346</t>
+          <t>286691</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330346</t>
+          <t>286691</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>330346</t>
+          <t>286691</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51243</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42263</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61141</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>43,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>40522</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>31466</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>50617</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55643</t>
+          <t>37804</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45876</t>
+          <t>29031</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67113</t>
+          <t>46807</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>96166</t>
+          <t>89047</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83446</t>
+          <t>76810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110607</t>
+          <t>104203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>90007</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80109</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>98987</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>63,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>56,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>70,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>102656</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>92561</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>111712</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>64,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>94609</t>
+          <t>105454</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83139</t>
+          <t>96451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104376</t>
+          <t>114227</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>197264</t>
+          <t>195461</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>182823</t>
+          <t>180305</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209984</t>
+          <t>207698</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>73,0%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>141250</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>141250</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>141250</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>143178</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>143178</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>143178</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>150252</t>
+          <t>143258</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>150252</t>
+          <t>143258</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>150252</t>
+          <t>143258</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>293430</t>
+          <t>284508</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>293430</t>
+          <t>284508</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>293430</t>
+          <t>284508</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>239119</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>214496</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>262239</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,32%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>43,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>163002</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>136345</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>185752</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>254601</t>
+          <t>155504</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>228801</t>
+          <t>139280</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>279715</t>
+          <t>173325</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>417604</t>
+          <t>394622</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>379725</t>
+          <t>366438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>453220</t>
+          <t>423257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>368183</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>345063</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>392806</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>56,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>64,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>567</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>412368</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>389618</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>439025</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>71,67%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>67,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>76,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>398251</t>
+          <t>389384</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>373137</t>
+          <t>371563</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424051</t>
+          <t>405608</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>810618</t>
+          <t>757568</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>775002</t>
+          <t>728933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>848497</t>
+          <t>785752</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>607302</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>607302</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>607302</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>801</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>575370</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>575370</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>575370</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>652852</t>
+          <t>544888</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>652852</t>
+          <t>544888</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>652852</t>
+          <t>544888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1228222</t>
+          <t>1152190</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1228222</t>
+          <t>1152190</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1228222</t>
+          <t>1152190</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
